--- a/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/continuation/conductor_1_coupling.xlsx
+++ b/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/continuation/conductor_1_coupling.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter_flag" sheetId="1" r:id="R2c3aa6b2fcfb44b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter" sheetId="2" r:id="R28879b19d47b41df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_choice" sheetId="3" r:id="R370a037a4a804f44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_HTC" sheetId="4" r:id="Rc96e410e428f4d7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="thermal_contact_resistance" sheetId="5" r:id="R0c8e41635d1247ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_multiplier" sheetId="6" r:id="Rfecdfb0187614d4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance_mode" sheetId="7" r:id="R375ab2e43a6a405b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance" sheetId="8" r:id="R590d8444d32c4a52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="open_perimeter_fract" sheetId="9" r:id="R36084d48fdbf4390"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="interf_thickness" sheetId="10" r:id="R8173f56a05504aae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trans_transp_multiplier" sheetId="11" r:id="R574506e4634e4ec3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="view_factors" sheetId="12" r:id="Rd53e3ce267974259"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter_flag" sheetId="1" r:id="R0cde1c00fb224bf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter" sheetId="2" r:id="Re74080fdc0c64ebf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_choice" sheetId="3" r:id="R4f68a55e82814480"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_HTC" sheetId="4" r:id="R858ab9050bca4cce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="thermal_contact_resistance" sheetId="5" r:id="R1cd65fd773e847ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_multiplier" sheetId="6" r:id="Ra9f2407af43a466b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance_mode" sheetId="7" r:id="R0ea8e371649146d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance" sheetId="8" r:id="Rda4c897ee281414f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="open_perimeter_fract" sheetId="9" r:id="R802d28f475ca426d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="interf_thickness" sheetId="10" r:id="R214b4a98f1c24816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trans_transp_multiplier" sheetId="11" r:id="Rcf210fda13184342"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="view_factors" sheetId="12" r:id="R7cfe75c5512b432c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1777,7 +1777,7 @@
       <x:c r="A1" s="6"/>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6" t="str">
-        <x:v>%[] flag to define the model to compute the HTC (yellow cells are those to thake into account). flag to decide how to evaluate interface htc.</x:v>
+        <x:v>%[] Flag used to select the HTC model (yellow cells are taken into account). This flag determines how the interface HTC is evaluated.</x:v>
       </x:c>
       <x:c r="D1" s="6"/>
       <x:c r="E1" s="6"/>
@@ -2943,7 +2943,7 @@
       <x:c r="A1" s="6"/>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6" t="str">
-        <x:v>Flag to specify the kind of electric conductance: 1 conductance per unit length (the contact is along a line as for tow cilinder); 2 = actual conductance between components.</x:v>
+        <x:v>Flag used to specify the electric conductance: 1 = conductance per unit length (the contact is along a line, as for two cylinders); 2 = actual conductance between components.</x:v>
       </x:c>
       <x:c r="D1" s="6"/>
       <x:c r="E1" s="6"/>
